--- a/8020-CutSheet.xlsx
+++ b/8020-CutSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorgft9510147-my.sharepoint.com/personal/dan_b-jetting_com/Documents/InternalShares/Educator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{DE3CDFE3-0FFF-4869-8A02-62930DD90B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEC98AF9-AE22-4EF6-A0B3-F595933E0AA5}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{DE3CDFE3-0FFF-4869-8A02-62930DD90B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62333EA2-2EA7-410E-93C1-040C1E02683F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="11890" windowWidth="19420" windowHeight="10300" xr2:uid="{389F9F36-A2B5-4CBA-B083-488EF3D0EE0B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{389F9F36-A2B5-4CBA-B083-488EF3D0EE0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="48">
   <si>
     <t>8020 Cut Sheet</t>
   </si>
@@ -168,6 +168,21 @@
   </si>
   <si>
     <t>14164 - M4 Drop-in Nut  QTY 25</t>
+  </si>
+  <si>
+    <t>25-2525-75  QTY 4 (Assembly Aid)</t>
+  </si>
+  <si>
+    <t>25-7051 in S @ 37.5</t>
+  </si>
+  <si>
+    <t>25-7051 in R @ 37.5</t>
+  </si>
+  <si>
+    <t>2.95 Inches (75 Millimeters) x $0.41</t>
+  </si>
+  <si>
+    <t>25-4118 3 Hole Joining Plate  QTY 2 (Assy Aid)</t>
   </si>
 </sst>
 </file>
@@ -199,7 +214,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -269,11 +284,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -286,6 +327,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AFC5DEB-BB3F-41D2-A944-B1DBA682A2BB}">
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
@@ -1175,6 +1218,112 @@
         <v>42</v>
       </c>
       <c r="B59" s="11"/>
+      <c r="D59" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E59" s="8"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D60" s="9"/>
+      <c r="E60" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D61" s="3"/>
+      <c r="E61" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D62" s="3"/>
+      <c r="E62" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D63" s="3"/>
+      <c r="E63" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D64" s="3"/>
+      <c r="E64" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D65" s="3"/>
+      <c r="E65" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D66" s="3"/>
+      <c r="E66" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D67" s="3"/>
+      <c r="E67" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D68" s="3"/>
+      <c r="E68" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D69" s="3"/>
+      <c r="E69" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D70" s="3"/>
+      <c r="E70" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D71" s="3"/>
+      <c r="E71" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D72" s="3"/>
+      <c r="E72" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="73" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D73" s="3"/>
+      <c r="E73" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D74" s="3"/>
+      <c r="E74" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D75" s="6"/>
+      <c r="E75" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D77" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E77" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
